--- a/data/dRevendas.xlsx
+++ b/data/dRevendas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caixa.patos\Documents\promax-web-driver\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cadcom.patos\Documents\promax-web-driver\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD2DF2B-73C9-4D34-BAB5-99A182E0C344}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D8BE85-6316-45B8-BA9D-54264860EE4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="33">
   <si>
     <t>SOUSA</t>
   </si>
@@ -127,6 +130,12 @@
   </si>
   <si>
     <t>BARRA</t>
+  </si>
+  <si>
+    <t>nomeUnidade030237estoque</t>
+  </si>
+  <si>
+    <t>nomeUnidade020502</t>
   </si>
 </sst>
 </file>
@@ -450,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.88671875" bestFit="1" customWidth="1"/>
@@ -458,10 +467,10 @@
     <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="12" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -492,9 +501,14 @@
       <c r="J1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>640001</v>
       </c>
@@ -525,9 +539,14 @@
       <c r="J2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="1"/>
+      <c r="K2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>640002</v>
       </c>
@@ -558,9 +577,14 @@
       <c r="J3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="1"/>
+      <c r="K3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2210003</v>
       </c>
@@ -591,9 +615,14 @@
       <c r="J4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="1"/>
+      <c r="K4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>2210004</v>
       </c>
@@ -624,9 +653,14 @@
       <c r="J5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K5" s="1"/>
+      <c r="K5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>3480005</v>
       </c>
@@ -657,9 +691,14 @@
       <c r="J6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K6" s="1"/>
+      <c r="K6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>3610006</v>
       </c>
@@ -690,9 +729,14 @@
       <c r="J7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="K7" s="1"/>
+      <c r="K7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3610007</v>
       </c>
@@ -723,9 +767,14 @@
       <c r="J8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K8" s="1"/>
+      <c r="K8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>3610008</v>
       </c>
@@ -756,7 +805,12 @@
       <c r="J9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K9" s="1"/>
+      <c r="K9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/dRevendas.xlsx
+++ b/data/dRevendas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cadcom.patos\Documents\promax-web-driver\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D8BE85-6316-45B8-BA9D-54264860EE4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41DBAF80-AC1F-485B-A830-7D59351E8B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="34">
   <si>
     <t>SOUSA</t>
   </si>
@@ -136,6 +136,9 @@
   </si>
   <si>
     <t>nomeUnidade020502</t>
+  </si>
+  <si>
+    <t>SUMÉ</t>
   </si>
 </sst>
 </file>
@@ -654,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="L5" s="1" t="s">
         <v>14</v>
